--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/解析结果/预案草稿/7.机房信息.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/解析结果/预案草稿/7.机房信息.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,106 @@
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>POD05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>POD06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>POD07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POD08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POD09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
